--- a/report_cards/Report_Card_Akinbile_Fausat.xlsx
+++ b/report_cards/Report_Card_Akinbile_Fausat.xlsx
@@ -1508,14 +1508,14 @@
       <c r="E28" s="35" t="n"/>
       <c r="F28" s="36" t="n"/>
       <c r="G28" s="42" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H28" s="42" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I28" s="36" t="n"/>
       <c r="J28" s="42" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K28" s="36" t="n"/>
       <c r="L28" s="18">
@@ -1572,11 +1572,11 @@
         <v>10</v>
       </c>
       <c r="H29" s="42" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I29" s="36" t="n"/>
       <c r="J29" s="42" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K29" s="36" t="n"/>
       <c r="L29" s="18">
@@ -1919,7 +1919,7 @@
         <v>13</v>
       </c>
       <c r="H36" s="42" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I36" s="36" t="n"/>
       <c r="J36" s="42" t="n">
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="X38" s="43" t="n">
-        <v>528</v>
+        <v>538</v>
       </c>
       <c r="Y38" s="30" t="n"/>
       <c r="Z38" s="30" t="n"/>
@@ -2031,14 +2031,14 @@
       <c r="E39" s="35" t="n"/>
       <c r="F39" s="36" t="n"/>
       <c r="G39" s="42" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H39" s="42" t="n">
         <v>14</v>
       </c>
       <c r="I39" s="36" t="n"/>
       <c r="J39" s="42" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K39" s="36" t="n"/>
       <c r="L39" s="18">
@@ -2064,7 +2064,7 @@
         </is>
       </c>
       <c r="X39" s="43" t="n">
-        <v>58.7</v>
+        <v>59.8</v>
       </c>
       <c r="Y39" s="30" t="n"/>
       <c r="Z39" s="30" t="n"/>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="X40" s="43" t="inlineStr">
         <is>
-          <t>58.67%</t>
+          <t>59.78%</t>
         </is>
       </c>
       <c r="Y40" s="30" t="n"/>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="X41" s="43" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="Y41" s="30" t="n"/>
@@ -2162,7 +2162,7 @@
         <v>12</v>
       </c>
       <c r="H42" s="42" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I42" s="36" t="n"/>
       <c r="J42" s="42" t="n">
@@ -2314,7 +2314,7 @@
         </is>
       </c>
       <c r="X45" s="43" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="Y45" s="30" t="n"/>
       <c r="Z45" s="30" t="n"/>
@@ -2426,7 +2426,7 @@
       <c r="E48" s="35" t="n"/>
       <c r="F48" s="36" t="n"/>
       <c r="G48" s="44" t="n">
-        <v>528</v>
+        <v>538</v>
       </c>
       <c r="H48" s="35" t="n"/>
       <c r="I48" s="35" t="n"/>
@@ -2458,7 +2458,7 @@
       <c r="E49" s="35" t="n"/>
       <c r="F49" s="36" t="n"/>
       <c r="G49" s="44" t="n">
-        <v>58.7</v>
+        <v>59.8</v>
       </c>
       <c r="H49" s="35" t="n"/>
       <c r="I49" s="35" t="n"/>
@@ -2491,7 +2491,7 @@
       <c r="F50" s="36" t="n"/>
       <c r="G50" s="44" t="inlineStr">
         <is>
-          <t>58.67%</t>
+          <t>59.78%</t>
         </is>
       </c>
       <c r="H50" s="35" t="n"/>
@@ -2525,7 +2525,7 @@
       <c r="F51" s="36" t="n"/>
       <c r="G51" s="44" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="H51" s="35" t="n"/>
@@ -2634,7 +2634,7 @@
       <c r="E55" s="35" t="n"/>
       <c r="F55" s="36" t="n"/>
       <c r="G55" s="44" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="H55" s="35" t="n"/>
       <c r="I55" s="35" t="n"/>

--- a/report_cards/Report_Card_Akinbile_Fausat.xlsx
+++ b/report_cards/Report_Card_Akinbile_Fausat.xlsx
@@ -1870,16 +1870,32 @@
       <c r="D35" s="35" t="n"/>
       <c r="E35" s="35" t="n"/>
       <c r="F35" s="36" t="n"/>
-      <c r="G35" s="18" t="inlineStr"/>
-      <c r="H35" s="18" t="inlineStr"/>
+      <c r="G35" s="42" t="n">
+        <v>14</v>
+      </c>
+      <c r="H35" s="42" t="n">
+        <v>21</v>
+      </c>
       <c r="I35" s="36" t="n"/>
-      <c r="J35" s="18" t="inlineStr"/>
+      <c r="J35" s="42" t="n">
+        <v>0</v>
+      </c>
       <c r="K35" s="36" t="n"/>
-      <c r="L35" s="18" t="inlineStr"/>
+      <c r="L35" s="18">
+        <f>SUM(G35, H35, J35)</f>
+        <v/>
+      </c>
       <c r="M35" s="36" t="n"/>
-      <c r="N35" s="18" t="inlineStr"/>
+      <c r="N35" s="18">
+        <f>IF(L35&gt;=75,"A1",IF(L35&gt;=70,"B2",IF(L35&gt;=65,"B3",IF(L35&gt;=60,"C4",IF(L35&gt;=55,"C5",IF(L35&gt;=50,"C6",IF(L35&gt;=45,"D7",IF(L35&gt;=40,"E8","F9"))))))))</f>
+        <v/>
+      </c>
       <c r="O35" s="36" t="n"/>
-      <c r="P35" s="18" t="inlineStr"/>
+      <c r="P35" s="42" t="inlineStr">
+        <is>
+          <t>8th</t>
+        </is>
+      </c>
       <c r="Q35" s="35" t="n"/>
       <c r="R35" s="36" t="n"/>
       <c r="T35" s="18" t="inlineStr">
@@ -2012,7 +2028,7 @@
         </is>
       </c>
       <c r="X38" s="43" t="n">
-        <v>538</v>
+        <v>573</v>
       </c>
       <c r="Y38" s="30" t="n"/>
       <c r="Z38" s="30" t="n"/>
@@ -2064,7 +2080,7 @@
         </is>
       </c>
       <c r="X39" s="43" t="n">
-        <v>59.8</v>
+        <v>57.3</v>
       </c>
       <c r="Y39" s="30" t="n"/>
       <c r="Z39" s="30" t="n"/>
@@ -2101,7 +2117,7 @@
       </c>
       <c r="X40" s="43" t="inlineStr">
         <is>
-          <t>59.78%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="Y40" s="30" t="n"/>
@@ -2139,7 +2155,7 @@
       </c>
       <c r="X41" s="43" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C5</t>
         </is>
       </c>
       <c r="Y41" s="30" t="n"/>
@@ -2314,7 +2330,7 @@
         </is>
       </c>
       <c r="X45" s="43" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="Y45" s="30" t="n"/>
       <c r="Z45" s="30" t="n"/>
@@ -2426,7 +2442,7 @@
       <c r="E48" s="35" t="n"/>
       <c r="F48" s="36" t="n"/>
       <c r="G48" s="44" t="n">
-        <v>538</v>
+        <v>573</v>
       </c>
       <c r="H48" s="35" t="n"/>
       <c r="I48" s="35" t="n"/>
@@ -2458,7 +2474,7 @@
       <c r="E49" s="35" t="n"/>
       <c r="F49" s="36" t="n"/>
       <c r="G49" s="44" t="n">
-        <v>59.8</v>
+        <v>57.3</v>
       </c>
       <c r="H49" s="35" t="n"/>
       <c r="I49" s="35" t="n"/>
@@ -2491,7 +2507,7 @@
       <c r="F50" s="36" t="n"/>
       <c r="G50" s="44" t="inlineStr">
         <is>
-          <t>59.78%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="H50" s="35" t="n"/>
@@ -2525,7 +2541,7 @@
       <c r="F51" s="36" t="n"/>
       <c r="G51" s="44" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C5</t>
         </is>
       </c>
       <c r="H51" s="35" t="n"/>
@@ -2634,7 +2650,7 @@
       <c r="E55" s="35" t="n"/>
       <c r="F55" s="36" t="n"/>
       <c r="G55" s="44" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="H55" s="35" t="n"/>
       <c r="I55" s="35" t="n"/>

--- a/report_cards/Report_Card_Akinbile_Fausat.xlsx
+++ b/report_cards/Report_Card_Akinbile_Fausat.xlsx
@@ -1871,14 +1871,14 @@
       <c r="E35" s="35" t="n"/>
       <c r="F35" s="36" t="n"/>
       <c r="G35" s="42" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="H35" s="42" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="I35" s="36" t="n"/>
       <c r="J35" s="42" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="K35" s="36" t="n"/>
       <c r="L35" s="18">
